--- a/diseases/d123/2026-2029.xlsx
+++ b/diseases/d123/2026-2029.xlsx
@@ -20213,16 +20213,16 @@
         </is>
       </c>
       <c r="N118" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O118" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q118" t="n">
         <v>0</v>
       </c>
       <c r="R118" t="n">
-        <v>0.03557618341728275</v>
+        <v>0.05336427512592412</v>
       </c>
       <c r="S118" t="inlineStr">
         <is>
@@ -20375,10 +20375,10 @@
         </is>
       </c>
       <c r="N119" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O119" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U119" t="inlineStr">
         <is>
@@ -24228,7 +24228,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d123/2026-2029.xlsx
+++ b/diseases/d123/2026-2029.xlsx
@@ -24050,6 +24050,154 @@
         </is>
       </c>
     </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>D123</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>tularemia</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>Tularemia</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>D123</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>Tularemia</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>土拉菌病</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L141" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N141" t="n">
+        <v>0</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0</v>
+      </c>
+      <c r="S141" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO141" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP141" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR141" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS141" t="inlineStr"/>
+      <c r="AT141" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU141" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV141" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW141" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX141" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY141" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ141" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA141" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB141" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC141" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -24083,7 +24231,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
     </row>
@@ -24166,7 +24314,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="10">
@@ -24176,7 +24324,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="11">

--- a/diseases/d123/2026-2029.xlsx
+++ b/diseases/d123/2026-2029.xlsx
@@ -913,9 +913,6 @@
       <c r="O3" t="n">
         <v>0</v>
       </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
       <c r="S3" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -1306,9 +1303,6 @@
       <c r="O5" t="n">
         <v>6</v>
       </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
       <c r="R5" t="n">
         <v>0.06660895370877544</v>
       </c>
@@ -1454,9 +1448,6 @@
       <c r="O6" t="n">
         <v>0</v>
       </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
       <c r="R6" t="n">
         <v>0</v>
       </c>
@@ -1850,9 +1841,6 @@
       <c r="O8" t="n">
         <v>0</v>
       </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
       <c r="R8" t="n">
         <v>0</v>
       </c>
@@ -1998,9 +1986,6 @@
       <c r="O9" t="n">
         <v>3</v>
       </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
       <c r="R9" t="n">
         <v>0.05306927477386519</v>
       </c>
@@ -2394,9 +2379,6 @@
       <c r="O11" t="n">
         <v>9</v>
       </c>
-      <c r="Q11" t="n">
-        <v>0</v>
-      </c>
       <c r="R11" t="n">
         <v>0.08410392385455011</v>
       </c>
@@ -4270,9 +4252,6 @@
       <c r="O23" t="n">
         <v>0</v>
       </c>
-      <c r="Q23" t="n">
-        <v>0</v>
-      </c>
       <c r="S23" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -4663,9 +4642,6 @@
       <c r="O25" t="n">
         <v>5</v>
       </c>
-      <c r="Q25" t="n">
-        <v>0</v>
-      </c>
       <c r="R25" t="n">
         <v>0.05550746142397953</v>
       </c>
@@ -4811,9 +4787,6 @@
       <c r="O26" t="n">
         <v>1</v>
       </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
       <c r="R26" t="n">
         <v>0.01778809170864137</v>
       </c>
@@ -5207,9 +5180,6 @@
       <c r="O28" t="n">
         <v>0</v>
       </c>
-      <c r="Q28" t="n">
-        <v>0</v>
-      </c>
       <c r="R28" t="n">
         <v>0</v>
       </c>
@@ -5355,9 +5325,6 @@
       <c r="O29" t="n">
         <v>4</v>
       </c>
-      <c r="Q29" t="n">
-        <v>0</v>
-      </c>
       <c r="R29" t="n">
         <v>0.07075903303182025</v>
       </c>
@@ -5751,9 +5718,6 @@
       <c r="O31" t="n">
         <v>8</v>
       </c>
-      <c r="Q31" t="n">
-        <v>0</v>
-      </c>
       <c r="R31" t="n">
         <v>0.07475904342626677</v>
       </c>
@@ -7479,9 +7443,6 @@
       <c r="O42" t="n">
         <v>0</v>
       </c>
-      <c r="Q42" t="n">
-        <v>0</v>
-      </c>
       <c r="S42" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -7872,9 +7833,6 @@
       <c r="O44" t="n">
         <v>6</v>
       </c>
-      <c r="Q44" t="n">
-        <v>0</v>
-      </c>
       <c r="R44" t="n">
         <v>0.06660895370877544</v>
       </c>
@@ -8020,9 +7978,6 @@
       <c r="O45" t="n">
         <v>0</v>
       </c>
-      <c r="Q45" t="n">
-        <v>0</v>
-      </c>
       <c r="R45" t="n">
         <v>0</v>
       </c>
@@ -8416,9 +8371,6 @@
       <c r="O47" t="n">
         <v>0</v>
       </c>
-      <c r="Q47" t="n">
-        <v>0</v>
-      </c>
       <c r="R47" t="n">
         <v>0</v>
       </c>
@@ -8564,9 +8516,6 @@
       <c r="O48" t="n">
         <v>1</v>
       </c>
-      <c r="Q48" t="n">
-        <v>0</v>
-      </c>
       <c r="R48" t="n">
         <v>0.01768975825795506</v>
       </c>
@@ -8960,9 +8909,6 @@
       <c r="O50" t="n">
         <v>5</v>
       </c>
-      <c r="Q50" t="n">
-        <v>0</v>
-      </c>
       <c r="R50" t="n">
         <v>0.04672440214141673</v>
       </c>
@@ -10540,9 +10486,6 @@
       <c r="O60" t="n">
         <v>0</v>
       </c>
-      <c r="Q60" t="n">
-        <v>0</v>
-      </c>
       <c r="R60" t="n">
         <v>0</v>
       </c>
@@ -10688,9 +10631,6 @@
       <c r="O61" t="n">
         <v>0</v>
       </c>
-      <c r="Q61" t="n">
-        <v>0</v>
-      </c>
       <c r="S61" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -11081,9 +11021,6 @@
       <c r="O63" t="n">
         <v>10</v>
       </c>
-      <c r="Q63" t="n">
-        <v>0</v>
-      </c>
       <c r="R63" t="n">
         <v>0.1110149228479591</v>
       </c>
@@ -11229,9 +11166,6 @@
       <c r="O64" t="n">
         <v>0</v>
       </c>
-      <c r="Q64" t="n">
-        <v>0</v>
-      </c>
       <c r="R64" t="n">
         <v>0</v>
       </c>
@@ -11625,9 +11559,6 @@
       <c r="O66" t="n">
         <v>0</v>
       </c>
-      <c r="Q66" t="n">
-        <v>0</v>
-      </c>
       <c r="R66" t="n">
         <v>0</v>
       </c>
@@ -11773,9 +11704,6 @@
       <c r="O67" t="n">
         <v>2</v>
       </c>
-      <c r="Q67" t="n">
-        <v>0</v>
-      </c>
       <c r="R67" t="n">
         <v>0.03537951651591013</v>
       </c>
@@ -12169,9 +12097,6 @@
       <c r="O69" t="n">
         <v>8</v>
       </c>
-      <c r="Q69" t="n">
-        <v>0</v>
-      </c>
       <c r="R69" t="n">
         <v>0.07475904342626677</v>
       </c>
@@ -13749,9 +13674,6 @@
       <c r="O79" t="n">
         <v>0</v>
       </c>
-      <c r="Q79" t="n">
-        <v>0</v>
-      </c>
       <c r="R79" t="n">
         <v>0</v>
       </c>
@@ -13897,9 +13819,6 @@
       <c r="O80" t="n">
         <v>0</v>
       </c>
-      <c r="Q80" t="n">
-        <v>0</v>
-      </c>
       <c r="S80" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -14290,9 +14209,6 @@
       <c r="O82" t="n">
         <v>19</v>
       </c>
-      <c r="Q82" t="n">
-        <v>0</v>
-      </c>
       <c r="R82" t="n">
         <v>0.2109283534111222</v>
       </c>
@@ -14438,9 +14354,6 @@
       <c r="O83" t="n">
         <v>1</v>
       </c>
-      <c r="Q83" t="n">
-        <v>0</v>
-      </c>
       <c r="R83" t="n">
         <v>0.01778809170864137</v>
       </c>
@@ -14834,9 +14747,6 @@
       <c r="O85" t="n">
         <v>0</v>
       </c>
-      <c r="Q85" t="n">
-        <v>0</v>
-      </c>
       <c r="R85" t="n">
         <v>0</v>
       </c>
@@ -14982,9 +14892,6 @@
       <c r="O86" t="n">
         <v>5</v>
       </c>
-      <c r="Q86" t="n">
-        <v>0</v>
-      </c>
       <c r="R86" t="n">
         <v>0.08844879128977531</v>
       </c>
@@ -15378,9 +15285,6 @@
       <c r="O88" t="n">
         <v>3</v>
       </c>
-      <c r="Q88" t="n">
-        <v>0</v>
-      </c>
       <c r="R88" t="n">
         <v>0.02803464128485004</v>
       </c>
@@ -17106,9 +17010,6 @@
       <c r="O99" t="n">
         <v>1</v>
       </c>
-      <c r="Q99" t="n">
-        <v>0</v>
-      </c>
       <c r="R99" t="n">
         <v>0.0002865038132769385</v>
       </c>
@@ -17254,9 +17155,6 @@
       <c r="O100" t="n">
         <v>0</v>
       </c>
-      <c r="Q100" t="n">
-        <v>0</v>
-      </c>
       <c r="R100" t="n">
         <v>0</v>
       </c>
@@ -17402,9 +17300,6 @@
       <c r="O101" t="n">
         <v>15</v>
       </c>
-      <c r="Q101" t="n">
-        <v>0</v>
-      </c>
       <c r="R101" t="n">
         <v>0.1665223842719386</v>
       </c>
@@ -17550,9 +17445,6 @@
       <c r="O102" t="n">
         <v>1</v>
       </c>
-      <c r="Q102" t="n">
-        <v>0</v>
-      </c>
       <c r="R102" t="n">
         <v>0.01778809170864137</v>
       </c>
@@ -17946,9 +17838,6 @@
       <c r="O104" t="n">
         <v>0</v>
       </c>
-      <c r="Q104" t="n">
-        <v>0</v>
-      </c>
       <c r="R104" t="n">
         <v>0</v>
       </c>
@@ -18094,9 +17983,6 @@
       <c r="O105" t="n">
         <v>7</v>
       </c>
-      <c r="Q105" t="n">
-        <v>0</v>
-      </c>
       <c r="R105" t="n">
         <v>0.1238283078056854</v>
       </c>
@@ -18490,9 +18376,6 @@
       <c r="O107" t="n">
         <v>9</v>
       </c>
-      <c r="Q107" t="n">
-        <v>0</v>
-      </c>
       <c r="R107" t="n">
         <v>0.08410392385455011</v>
       </c>
@@ -18886,9 +18769,6 @@
       <c r="O109" t="n">
         <v>0</v>
       </c>
-      <c r="Q109" t="n">
-        <v>0</v>
-      </c>
       <c r="R109" t="n">
         <v>0</v>
       </c>
@@ -19034,9 +18914,6 @@
       <c r="O110" t="n">
         <v>1</v>
       </c>
-      <c r="Q110" t="n">
-        <v>0</v>
-      </c>
       <c r="R110" t="n">
         <v>0.0002865038132769385</v>
       </c>
@@ -19182,9 +19059,6 @@
       <c r="O111" t="n">
         <v>0</v>
       </c>
-      <c r="Q111" t="n">
-        <v>0</v>
-      </c>
       <c r="R111" t="n">
         <v>0</v>
       </c>
@@ -19330,9 +19204,6 @@
       <c r="O112" t="n">
         <v>0</v>
       </c>
-      <c r="Q112" t="n">
-        <v>0</v>
-      </c>
       <c r="R112" t="n">
         <v>0</v>
       </c>
@@ -19478,9 +19349,6 @@
       <c r="O113" t="n">
         <v>0</v>
       </c>
-      <c r="Q113" t="n">
-        <v>0</v>
-      </c>
       <c r="R113" t="n">
         <v>0</v>
       </c>
@@ -19626,9 +19494,6 @@
       <c r="O114" t="n">
         <v>2</v>
       </c>
-      <c r="Q114" t="n">
-        <v>0</v>
-      </c>
       <c r="R114" t="n">
         <v>0.0005730076265538771</v>
       </c>
@@ -19774,9 +19639,6 @@
       <c r="O115" t="n">
         <v>0</v>
       </c>
-      <c r="Q115" t="n">
-        <v>0</v>
-      </c>
       <c r="R115" t="n">
         <v>0</v>
       </c>
@@ -19922,9 +19784,6 @@
       <c r="O116" t="n">
         <v>1</v>
       </c>
-      <c r="Q116" t="n">
-        <v>0</v>
-      </c>
       <c r="R116" t="n">
         <v>0.0002865038132769385</v>
       </c>
@@ -20070,9 +19929,6 @@
       <c r="O117" t="n">
         <v>0</v>
       </c>
-      <c r="Q117" t="n">
-        <v>0</v>
-      </c>
       <c r="R117" t="n">
         <v>0</v>
       </c>
@@ -20213,16 +20069,13 @@
         </is>
       </c>
       <c r="N118" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O118" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q118" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R118" t="n">
-        <v>0.05336427512592412</v>
+        <v>0.07115236683456549</v>
       </c>
       <c r="S118" t="inlineStr">
         <is>
@@ -20375,10 +20228,10 @@
         </is>
       </c>
       <c r="N119" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O119" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="U119" t="inlineStr">
         <is>
@@ -20614,9 +20467,6 @@
       <c r="O120" t="n">
         <v>0</v>
       </c>
-      <c r="Q120" t="n">
-        <v>0</v>
-      </c>
       <c r="R120" t="n">
         <v>0</v>
       </c>
@@ -20757,16 +20607,13 @@
         </is>
       </c>
       <c r="N121" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="O121" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q121" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="R121" t="n">
-        <v>0.1768975825795506</v>
+        <v>0.1945873408375057</v>
       </c>
       <c r="S121" t="inlineStr">
         <is>
@@ -20919,10 +20766,10 @@
         </is>
       </c>
       <c r="N122" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="O122" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="U122" t="inlineStr">
         <is>
@@ -21158,9 +21005,6 @@
       <c r="O123" t="n">
         <v>45</v>
       </c>
-      <c r="Q123" t="n">
-        <v>0</v>
-      </c>
       <c r="R123" t="n">
         <v>0.4205196192727506</v>
       </c>
@@ -21554,9 +21398,6 @@
       <c r="O125" t="n">
         <v>0</v>
       </c>
-      <c r="Q125" t="n">
-        <v>0</v>
-      </c>
       <c r="R125" t="n">
         <v>0</v>
       </c>
@@ -21702,9 +21543,6 @@
       <c r="O126" t="n">
         <v>3</v>
       </c>
-      <c r="Q126" t="n">
-        <v>0</v>
-      </c>
       <c r="R126" t="n">
         <v>0.0008595114398308156</v>
       </c>
@@ -21850,9 +21688,6 @@
       <c r="O127" t="n">
         <v>0</v>
       </c>
-      <c r="Q127" t="n">
-        <v>0</v>
-      </c>
       <c r="R127" t="n">
         <v>0</v>
       </c>
@@ -21998,9 +21833,6 @@
       <c r="O128" t="n">
         <v>2</v>
       </c>
-      <c r="Q128" t="n">
-        <v>0</v>
-      </c>
       <c r="R128" t="n">
         <v>0.0005730076265538771</v>
       </c>
@@ -22146,9 +21978,6 @@
       <c r="O129" t="n">
         <v>0</v>
       </c>
-      <c r="Q129" t="n">
-        <v>0</v>
-      </c>
       <c r="R129" t="n">
         <v>0</v>
       </c>
@@ -22294,9 +22123,6 @@
       <c r="O130" t="n">
         <v>2</v>
       </c>
-      <c r="Q130" t="n">
-        <v>0</v>
-      </c>
       <c r="R130" t="n">
         <v>0.0005730076265538771</v>
       </c>
@@ -22442,9 +22268,6 @@
       <c r="O131" t="n">
         <v>0</v>
       </c>
-      <c r="Q131" t="n">
-        <v>0</v>
-      </c>
       <c r="R131" t="n">
         <v>0</v>
       </c>
@@ -22590,9 +22413,6 @@
       <c r="O132" t="n">
         <v>0</v>
       </c>
-      <c r="Q132" t="n">
-        <v>0</v>
-      </c>
       <c r="R132" t="n">
         <v>0</v>
       </c>
@@ -22738,9 +22558,6 @@
       <c r="O133" t="n">
         <v>0</v>
       </c>
-      <c r="Q133" t="n">
-        <v>0</v>
-      </c>
       <c r="R133" t="n">
         <v>0</v>
       </c>
@@ -22886,9 +22703,6 @@
       <c r="O134" t="n">
         <v>0</v>
       </c>
-      <c r="Q134" t="n">
-        <v>0</v>
-      </c>
       <c r="R134" t="n">
         <v>0</v>
       </c>
@@ -23034,9 +22848,6 @@
       <c r="O135" t="n">
         <v>0</v>
       </c>
-      <c r="Q135" t="n">
-        <v>0</v>
-      </c>
       <c r="R135" t="n">
         <v>0</v>
       </c>
@@ -23430,9 +23241,6 @@
       <c r="O137" t="n">
         <v>0</v>
       </c>
-      <c r="Q137" t="n">
-        <v>0</v>
-      </c>
       <c r="R137" t="n">
         <v>0</v>
       </c>
@@ -23573,16 +23381,13 @@
         </is>
       </c>
       <c r="N138" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O138" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q138" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R138" t="n">
-        <v>0</v>
+        <v>0.03537951651591013</v>
       </c>
       <c r="S138" t="inlineStr">
         <is>
@@ -23735,10 +23540,10 @@
         </is>
       </c>
       <c r="N139" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O139" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U139" t="inlineStr">
         <is>
@@ -23974,9 +23779,6 @@
       <c r="O140" t="n">
         <v>2</v>
       </c>
-      <c r="Q140" t="n">
-        <v>0</v>
-      </c>
       <c r="R140" t="n">
         <v>0.0005730076265538771</v>
       </c>
@@ -24122,9 +23924,6 @@
       <c r="O141" t="n">
         <v>0</v>
       </c>
-      <c r="Q141" t="n">
-        <v>0</v>
-      </c>
       <c r="R141" t="n">
         <v>0</v>
       </c>
@@ -24195,6 +23994,151 @@
       <c r="BC141" t="inlineStr">
         <is>
           <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>D123</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>tularemia</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>Tularemia</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>D123</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>Tularemia</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>土拉菌病</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L142" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="M142" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N142" t="n">
+        <v>2</v>
+      </c>
+      <c r="O142" t="n">
+        <v>2</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.0005730076265538771</v>
+      </c>
+      <c r="S142" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO142" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP142" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR142" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS142" t="inlineStr"/>
+      <c r="AT142" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU142" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV142" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW142" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX142" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY142" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ142" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA142" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB142" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC142" t="inlineStr">
+        <is>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -24231,7 +24175,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-08</t>
         </is>
       </c>
     </row>
@@ -24314,7 +24258,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="10">
@@ -24324,7 +24268,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="11">
@@ -24376,7 +24320,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>205</v>
+        <v>211</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d123/2026-2029.xlsx
+++ b/diseases/d123/2026-2029.xlsx
@@ -22843,13 +22843,13 @@
         </is>
       </c>
       <c r="N135" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O135" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R135" t="n">
-        <v>0</v>
+        <v>0.01778809170864137</v>
       </c>
       <c r="S135" t="inlineStr">
         <is>
@@ -23002,10 +23002,10 @@
         </is>
       </c>
       <c r="N136" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O136" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U136" t="inlineStr">
         <is>
@@ -24320,7 +24320,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d123/2026-2029.xlsx
+++ b/diseases/d123/2026-2029.xlsx
@@ -17256,12 +17256,12 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>CH</t>
+          <t>CA-ON</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>Ontario, Canada</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -17295,81 +17295,92 @@
         </is>
       </c>
       <c r="N101" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="O101" t="n">
-        <v>15</v>
-      </c>
-      <c r="R101" t="n">
-        <v>0.1665223842719386</v>
+        <v>0</v>
       </c>
       <c r="S101" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U101" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_TULAREMIA_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO101" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP101" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR101" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS101" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ101" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS101" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_TULAREMIA_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT101" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU101" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV101" t="inlineStr">
         <is>
-          <t>foph_idd</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Switzerland FOPH IDD</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr">
         <is>
-          <t>rest_api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ101" t="inlineStr">
         <is>
-          <t>foph_idd</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="BA101" t="inlineStr">
         <is>
-          <t>Switzerland FOPH IDD</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="BB101" t="inlineStr">
         <is>
-          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="BC101" t="inlineStr">
         <is>
-          <t>rest_api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -17396,17 +17407,17 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CA-ON</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Ontario, Canada</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -17440,29 +17451,104 @@
         </is>
       </c>
       <c r="N102" t="n">
+        <v>0</v>
+      </c>
+      <c r="O102" t="n">
+        <v>0</v>
+      </c>
+      <c r="U102" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_TULAREMIA_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V102" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_TULAREMIA_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W102" t="inlineStr">
+        <is>
+          <t>SRC_CA_ON_PHO_IDTO</t>
+        </is>
+      </c>
+      <c r="X102" t="inlineStr">
+        <is>
+          <t>Tularemia</t>
+        </is>
+      </c>
+      <c r="Y102" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z102" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA102" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB102" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC102" t="inlineStr">
+        <is>
+          <t>country:CA-ON:national</t>
+        </is>
+      </c>
+      <c r="AD102" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE102" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF102" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG102" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH102" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI102" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ102" t="inlineStr">
+        <is>
+          <t>PHO_IDTO_2026_07</t>
+        </is>
+      </c>
+      <c r="AK102" t="inlineStr">
+        <is>
+          <t>PHO IDTO current-year monthly preliminary tularemia notifications; confirmed cases only under the July 2026 technical notes.</t>
+        </is>
+      </c>
+      <c r="AM102" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN102" t="b">
         <v>1</v>
       </c>
-      <c r="O102" t="n">
-        <v>1</v>
-      </c>
-      <c r="R102" t="n">
-        <v>0.01778809170864137</v>
-      </c>
-      <c r="S102" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U102" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1540</t>
-        </is>
-      </c>
-      <c r="AA102" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO102" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -17475,12 +17561,12 @@
       </c>
       <c r="AQ102" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS102" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1540</t>
+          <t>SER_CA_ON_PHO_IDTO_TULAREMIA_MONTHLY</t>
         </is>
       </c>
       <c r="AT102" t="n">
@@ -17488,47 +17574,47 @@
       </c>
       <c r="AU102" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV102" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ102" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="BA102" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="BB102" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="BC102" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -17555,17 +17641,17 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -17599,170 +17685,81 @@
         </is>
       </c>
       <c r="N103" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="O103" t="n">
-        <v>1</v>
-      </c>
-      <c r="U103" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1540</t>
-        </is>
-      </c>
-      <c r="V103" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1540</t>
-        </is>
-      </c>
-      <c r="W103" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X103" t="inlineStr">
-        <is>
-          <t>Tularaemia (rabbit fever)</t>
-        </is>
-      </c>
-      <c r="Y103" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z103" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA103" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB103" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC103" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD103" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE103" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF103" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG103" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH103" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI103" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ103" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK103" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 1540.</t>
-        </is>
-      </c>
-      <c r="AM103" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN103" t="b">
-        <v>1</v>
+        <v>15</v>
+      </c>
+      <c r="R103" t="n">
+        <v>0.1665223842719386</v>
+      </c>
+      <c r="S103" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO103" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP103" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ103" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS103" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1540</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR103" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS103" t="inlineStr"/>
       <c r="AT103" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU103" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV103" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>foph_idd</t>
         </is>
       </c>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Switzerland FOPH IDD</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>rest_api</t>
         </is>
       </c>
       <c r="AZ103" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>foph_idd</t>
         </is>
       </c>
       <c r="BA103" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Switzerland FOPH IDD</t>
         </is>
       </c>
       <c r="BB103" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
         </is>
       </c>
       <c r="BC103" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>rest_api</t>
         </is>
       </c>
     </row>
@@ -17794,12 +17791,12 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -17833,81 +17830,95 @@
         </is>
       </c>
       <c r="N104" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O104" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R104" t="n">
-        <v>0</v>
+        <v>0.01778809170864137</v>
       </c>
       <c r="S104" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U104" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1540</t>
+        </is>
+      </c>
+      <c r="AA104" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO104" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP104" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR104" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS104" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ104" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS104" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1540</t>
+        </is>
+      </c>
       <c r="AT104" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU104" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV104" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ104" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA104" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB104" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC104" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -17934,17 +17945,17 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -17978,22 +17989,39 @@
         </is>
       </c>
       <c r="N105" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="O105" t="n">
-        <v>7</v>
-      </c>
-      <c r="R105" t="n">
-        <v>0.1238283078056854</v>
-      </c>
-      <c r="S105" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="U105" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_403_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1540</t>
+        </is>
+      </c>
+      <c r="V105" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1540</t>
+        </is>
+      </c>
+      <c r="W105" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X105" t="inlineStr">
+        <is>
+          <t>Tularaemia (rabbit fever)</t>
+        </is>
+      </c>
+      <c r="Y105" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z105" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -18001,6 +18029,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB105" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC105" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD105" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE105" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF105" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG105" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH105" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI105" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ105" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK105" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 1540.</t>
+        </is>
+      </c>
+      <c r="AM105" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN105" t="b">
+        <v>1</v>
+      </c>
       <c r="AO105" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -18013,12 +18099,12 @@
       </c>
       <c r="AQ105" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS105" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_403_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1540</t>
         </is>
       </c>
       <c r="AT105" t="n">
@@ -18026,47 +18112,47 @@
       </c>
       <c r="AU105" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV105" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ105" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA105" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB105" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC105" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -18093,17 +18179,17 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -18137,170 +18223,81 @@
         </is>
       </c>
       <c r="N106" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="O106" t="n">
-        <v>7</v>
-      </c>
-      <c r="U106" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_403_MONTHLY</t>
-        </is>
-      </c>
-      <c r="V106" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_403_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W106" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X106" t="inlineStr">
-        <is>
-          <t>Tularemi</t>
-        </is>
-      </c>
-      <c r="Y106" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z106" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA106" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB106" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC106" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD106" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE106" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF106" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG106" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH106" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI106" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ106" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK106" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM106" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN106" t="b">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="R106" t="n">
+        <v>0</v>
+      </c>
+      <c r="S106" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO106" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP106" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ106" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS106" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_403_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR106" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS106" t="inlineStr"/>
       <c r="AT106" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU106" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV106" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ106" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA106" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB106" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC106" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -18332,12 +18329,12 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -18371,13 +18368,13 @@
         </is>
       </c>
       <c r="N107" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="O107" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="R107" t="n">
-        <v>0.08410392385455011</v>
+        <v>0.1238283078056854</v>
       </c>
       <c r="S107" t="inlineStr">
         <is>
@@ -18386,7 +18383,7 @@
       </c>
       <c r="U107" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_TULAREMIA</t>
+          <t>SER_NO_FHI_403_MONTHLY</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -18411,7 +18408,7 @@
       </c>
       <c r="AS107" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_TULAREMIA</t>
+          <t>SER_NO_FHI_403_MONTHLY</t>
         </is>
       </c>
       <c r="AT107" t="n">
@@ -18424,42 +18421,42 @@
       </c>
       <c r="AV107" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ107" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA107" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB107" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC107" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -18491,12 +18488,12 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -18530,29 +18527,29 @@
         </is>
       </c>
       <c r="N108" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="O108" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="U108" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_TULAREMIA</t>
+          <t>SER_NO_FHI_403_MONTHLY</t>
         </is>
       </c>
       <c r="V108" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_TULAREMIA</t>
+          <t>SER_NO_FHI_403_MONTHLY</t>
         </is>
       </c>
       <c r="W108" t="inlineStr">
         <is>
-          <t>SRC_SE_FOHM_SMINET</t>
+          <t>SRC_NO_FHI_MSIS</t>
         </is>
       </c>
       <c r="X108" t="inlineStr">
         <is>
-          <t>Harpest</t>
+          <t>Tularemi</t>
         </is>
       </c>
       <c r="Y108" t="inlineStr">
@@ -18577,7 +18574,7 @@
       </c>
       <c r="AC108" t="inlineStr">
         <is>
-          <t>country:SE:national</t>
+          <t>country:NO:national</t>
         </is>
       </c>
       <c r="AD108" t="inlineStr">
@@ -18612,17 +18609,17 @@
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>SE_FOHM_SMINET_current</t>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
         </is>
       </c>
       <c r="AK108" t="inlineStr">
         <is>
-          <t>Sweden FHM SmiNet national monthly notification series; FHM tularemia category.</t>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
         </is>
       </c>
       <c r="AM108" t="inlineStr">
         <is>
-          <t>revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN108" t="b">
@@ -18645,7 +18642,7 @@
       </c>
       <c r="AS108" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_TULAREMIA</t>
+          <t>SER_NO_FHI_403_MONTHLY</t>
         </is>
       </c>
       <c r="AT108" t="n">
@@ -18658,42 +18655,42 @@
       </c>
       <c r="AV108" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ108" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA108" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB108" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC108" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -18725,12 +18722,12 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -18755,7 +18752,7 @@
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M109" t="inlineStr">
@@ -18764,81 +18761,95 @@
         </is>
       </c>
       <c r="N109" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="O109" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="R109" t="n">
-        <v>0</v>
+        <v>0.08410392385455011</v>
       </c>
       <c r="S109" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U109" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_TULAREMIA</t>
+        </is>
+      </c>
+      <c r="AA109" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO109" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP109" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR109" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS109" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ109" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS109" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_TULAREMIA</t>
+        </is>
+      </c>
       <c r="AT109" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU109" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV109" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ109" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA109" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB109" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC109" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -18865,17 +18876,17 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -18900,7 +18911,7 @@
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M110" t="inlineStr">
@@ -18909,81 +18920,170 @@
         </is>
       </c>
       <c r="N110" t="n">
+        <v>9</v>
+      </c>
+      <c r="O110" t="n">
+        <v>9</v>
+      </c>
+      <c r="U110" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_TULAREMIA</t>
+        </is>
+      </c>
+      <c r="V110" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_TULAREMIA</t>
+        </is>
+      </c>
+      <c r="W110" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X110" t="inlineStr">
+        <is>
+          <t>Harpest</t>
+        </is>
+      </c>
+      <c r="Y110" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z110" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA110" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB110" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC110" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD110" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE110" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF110" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG110" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH110" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI110" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ110" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK110" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM tularemia category.</t>
+        </is>
+      </c>
+      <c r="AM110" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN110" t="b">
         <v>1</v>
       </c>
-      <c r="O110" t="n">
+      <c r="AO110" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP110" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ110" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS110" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_TULAREMIA</t>
+        </is>
+      </c>
+      <c r="AT110" t="n">
         <v>1</v>
       </c>
-      <c r="R110" t="n">
-        <v>0.0002865038132769385</v>
-      </c>
-      <c r="S110" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AO110" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP110" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR110" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS110" t="inlineStr"/>
-      <c r="AT110" t="n">
-        <v>0</v>
-      </c>
       <c r="AU110" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV110" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ110" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA110" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB110" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC110" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -19045,7 +19145,7 @@
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="M111" t="inlineStr">
@@ -19190,7 +19290,7 @@
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="M112" t="inlineStr">
@@ -19199,13 +19299,13 @@
         </is>
       </c>
       <c r="N112" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O112" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R112" t="n">
-        <v>0</v>
+        <v>0.0002865038132769385</v>
       </c>
       <c r="S112" t="inlineStr">
         <is>
@@ -19335,7 +19435,7 @@
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="M113" t="inlineStr">
@@ -19480,7 +19580,7 @@
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="M114" t="inlineStr">
@@ -19489,13 +19589,13 @@
         </is>
       </c>
       <c r="N114" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O114" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R114" t="n">
-        <v>0.0005730076265538771</v>
+        <v>0</v>
       </c>
       <c r="S114" t="inlineStr">
         <is>
@@ -19625,7 +19725,7 @@
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="M115" t="inlineStr">
@@ -19770,7 +19870,7 @@
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="M116" t="inlineStr">
@@ -19779,13 +19879,13 @@
         </is>
       </c>
       <c r="N116" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O116" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R116" t="n">
-        <v>0.0002865038132769385</v>
+        <v>0.0005730076265538771</v>
       </c>
       <c r="S116" t="inlineStr">
         <is>
@@ -19885,12 +19985,12 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -19915,12 +20015,12 @@
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N117" t="n">
@@ -19963,42 +20063,42 @@
       </c>
       <c r="AV117" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ117" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA117" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB117" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC117" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -20030,12 +20130,12 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -20060,104 +20160,90 @@
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N118" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O118" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="R118" t="n">
-        <v>0.07115236683456549</v>
+        <v>0.0002865038132769385</v>
       </c>
       <c r="S118" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U118" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1540</t>
-        </is>
-      </c>
-      <c r="AA118" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO118" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP118" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ118" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS118" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1540</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR118" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS118" t="inlineStr"/>
       <c r="AT118" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU118" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV118" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ118" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA118" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB118" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC118" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -20184,17 +20270,17 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -20228,170 +20314,81 @@
         </is>
       </c>
       <c r="N119" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O119" t="n">
-        <v>4</v>
-      </c>
-      <c r="U119" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1540</t>
-        </is>
-      </c>
-      <c r="V119" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1540</t>
-        </is>
-      </c>
-      <c r="W119" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X119" t="inlineStr">
-        <is>
-          <t>Tularaemia (rabbit fever)</t>
-        </is>
-      </c>
-      <c r="Y119" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z119" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA119" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB119" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC119" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD119" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0</v>
+      </c>
+      <c r="S119" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO119" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP119" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR119" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS119" t="inlineStr"/>
+      <c r="AT119" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU119" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV119" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE119" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF119" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG119" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH119" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI119" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ119" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK119" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 1540.</t>
-        </is>
-      </c>
-      <c r="AM119" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN119" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO119" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP119" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ119" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS119" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1540</t>
-        </is>
-      </c>
-      <c r="AT119" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU119" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
-        </is>
-      </c>
-      <c r="AV119" t="inlineStr">
-        <is>
-          <t>thl_ttr</t>
-        </is>
-      </c>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ119" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA119" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB119" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC119" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -20423,12 +20420,12 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -20462,81 +20459,95 @@
         </is>
       </c>
       <c r="N120" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O120" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R120" t="n">
-        <v>0</v>
+        <v>0.07115236683456549</v>
       </c>
       <c r="S120" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U120" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1540</t>
+        </is>
+      </c>
+      <c r="AA120" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO120" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP120" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR120" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS120" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ120" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS120" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1540</t>
+        </is>
+      </c>
       <c r="AT120" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU120" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV120" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ120" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA120" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB120" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC120" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -20563,17 +20574,17 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -20607,22 +20618,39 @@
         </is>
       </c>
       <c r="N121" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="O121" t="n">
-        <v>11</v>
-      </c>
-      <c r="R121" t="n">
-        <v>0.1945873408375057</v>
-      </c>
-      <c r="S121" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>4</v>
       </c>
       <c r="U121" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_403_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1540</t>
+        </is>
+      </c>
+      <c r="V121" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1540</t>
+        </is>
+      </c>
+      <c r="W121" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X121" t="inlineStr">
+        <is>
+          <t>Tularaemia (rabbit fever)</t>
+        </is>
+      </c>
+      <c r="Y121" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z121" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -20630,6 +20658,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB121" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC121" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD121" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE121" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF121" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG121" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH121" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI121" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ121" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK121" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 1540.</t>
+        </is>
+      </c>
+      <c r="AM121" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN121" t="b">
+        <v>1</v>
+      </c>
       <c r="AO121" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -20642,12 +20728,12 @@
       </c>
       <c r="AQ121" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS121" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_403_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1540</t>
         </is>
       </c>
       <c r="AT121" t="n">
@@ -20655,47 +20741,47 @@
       </c>
       <c r="AU121" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV121" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ121" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA121" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB121" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC121" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -20722,17 +20808,17 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -20766,170 +20852,81 @@
         </is>
       </c>
       <c r="N122" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="O122" t="n">
-        <v>11</v>
-      </c>
-      <c r="U122" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_403_MONTHLY</t>
-        </is>
-      </c>
-      <c r="V122" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_403_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W122" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X122" t="inlineStr">
-        <is>
-          <t>Tularemi</t>
-        </is>
-      </c>
-      <c r="Y122" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z122" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA122" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB122" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC122" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD122" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE122" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF122" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG122" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH122" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI122" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ122" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK122" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM122" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN122" t="b">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0</v>
+      </c>
+      <c r="S122" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO122" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP122" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ122" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS122" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_403_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR122" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS122" t="inlineStr"/>
       <c r="AT122" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU122" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV122" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ122" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA122" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB122" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC122" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -20961,12 +20958,12 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -21000,13 +20997,13 @@
         </is>
       </c>
       <c r="N123" t="n">
-        <v>45</v>
+        <v>11</v>
       </c>
       <c r="O123" t="n">
-        <v>45</v>
+        <v>11</v>
       </c>
       <c r="R123" t="n">
-        <v>0.4205196192727506</v>
+        <v>0.1945873408375057</v>
       </c>
       <c r="S123" t="inlineStr">
         <is>
@@ -21015,7 +21012,7 @@
       </c>
       <c r="U123" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_TULAREMIA</t>
+          <t>SER_NO_FHI_403_MONTHLY</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -21040,7 +21037,7 @@
       </c>
       <c r="AS123" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_TULAREMIA</t>
+          <t>SER_NO_FHI_403_MONTHLY</t>
         </is>
       </c>
       <c r="AT123" t="n">
@@ -21053,42 +21050,42 @@
       </c>
       <c r="AV123" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ123" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA123" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB123" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC123" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -21120,12 +21117,12 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -21159,29 +21156,29 @@
         </is>
       </c>
       <c r="N124" t="n">
-        <v>45</v>
+        <v>11</v>
       </c>
       <c r="O124" t="n">
-        <v>45</v>
+        <v>11</v>
       </c>
       <c r="U124" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_TULAREMIA</t>
+          <t>SER_NO_FHI_403_MONTHLY</t>
         </is>
       </c>
       <c r="V124" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_TULAREMIA</t>
+          <t>SER_NO_FHI_403_MONTHLY</t>
         </is>
       </c>
       <c r="W124" t="inlineStr">
         <is>
-          <t>SRC_SE_FOHM_SMINET</t>
+          <t>SRC_NO_FHI_MSIS</t>
         </is>
       </c>
       <c r="X124" t="inlineStr">
         <is>
-          <t>Harpest</t>
+          <t>Tularemi</t>
         </is>
       </c>
       <c r="Y124" t="inlineStr">
@@ -21206,7 +21203,7 @@
       </c>
       <c r="AC124" t="inlineStr">
         <is>
-          <t>country:SE:national</t>
+          <t>country:NO:national</t>
         </is>
       </c>
       <c r="AD124" t="inlineStr">
@@ -21241,17 +21238,17 @@
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>SE_FOHM_SMINET_current</t>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
         </is>
       </c>
       <c r="AK124" t="inlineStr">
         <is>
-          <t>Sweden FHM SmiNet national monthly notification series; FHM tularemia category.</t>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
         </is>
       </c>
       <c r="AM124" t="inlineStr">
         <is>
-          <t>revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN124" t="b">
@@ -21274,7 +21271,7 @@
       </c>
       <c r="AS124" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_TULAREMIA</t>
+          <t>SER_NO_FHI_403_MONTHLY</t>
         </is>
       </c>
       <c r="AT124" t="n">
@@ -21287,42 +21284,42 @@
       </c>
       <c r="AV124" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ124" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA124" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB124" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC124" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -21354,12 +21351,12 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -21384,7 +21381,7 @@
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M125" t="inlineStr">
@@ -21393,81 +21390,95 @@
         </is>
       </c>
       <c r="N125" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="O125" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="R125" t="n">
-        <v>0</v>
+        <v>0.4205196192727506</v>
       </c>
       <c r="S125" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U125" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_TULAREMIA</t>
+        </is>
+      </c>
+      <c r="AA125" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO125" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP125" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR125" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS125" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ125" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS125" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_TULAREMIA</t>
+        </is>
+      </c>
       <c r="AT125" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU125" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV125" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ125" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA125" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB125" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC125" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -21494,17 +21505,17 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -21529,7 +21540,7 @@
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M126" t="inlineStr">
@@ -21538,81 +21549,170 @@
         </is>
       </c>
       <c r="N126" t="n">
-        <v>3</v>
+        <v>45</v>
       </c>
       <c r="O126" t="n">
-        <v>3</v>
-      </c>
-      <c r="R126" t="n">
-        <v>0.0008595114398308156</v>
-      </c>
-      <c r="S126" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>45</v>
+      </c>
+      <c r="U126" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_TULAREMIA</t>
+        </is>
+      </c>
+      <c r="V126" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_TULAREMIA</t>
+        </is>
+      </c>
+      <c r="W126" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X126" t="inlineStr">
+        <is>
+          <t>Harpest</t>
+        </is>
+      </c>
+      <c r="Y126" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z126" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA126" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB126" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC126" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD126" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE126" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF126" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG126" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH126" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI126" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ126" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK126" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM tularemia category.</t>
+        </is>
+      </c>
+      <c r="AM126" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN126" t="b">
+        <v>1</v>
       </c>
       <c r="AO126" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP126" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR126" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS126" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ126" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS126" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_TULAREMIA</t>
+        </is>
+      </c>
       <c r="AT126" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU126" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV126" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ126" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA126" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB126" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC126" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -21674,7 +21774,7 @@
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="M127" t="inlineStr">
@@ -21819,7 +21919,7 @@
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="M128" t="inlineStr">
@@ -21828,13 +21928,13 @@
         </is>
       </c>
       <c r="N128" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O128" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R128" t="n">
-        <v>0.0005730076265538771</v>
+        <v>0.0008595114398308156</v>
       </c>
       <c r="S128" t="inlineStr">
         <is>
@@ -21964,7 +22064,7 @@
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="M129" t="inlineStr">
@@ -22109,7 +22209,7 @@
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="M130" t="inlineStr">
@@ -22254,7 +22354,7 @@
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="M131" t="inlineStr">
@@ -22399,7 +22499,7 @@
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="M132" t="inlineStr">
@@ -22408,13 +22508,13 @@
         </is>
       </c>
       <c r="N132" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O132" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R132" t="n">
-        <v>0</v>
+        <v>0.0005730076265538771</v>
       </c>
       <c r="S132" t="inlineStr">
         <is>
@@ -22544,7 +22644,7 @@
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="M133" t="inlineStr">
@@ -22659,12 +22759,12 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -22689,12 +22789,12 @@
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N134" t="n">
@@ -22737,42 +22837,42 @@
       </c>
       <c r="AV134" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ134" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA134" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB134" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC134" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -22804,12 +22904,12 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -22834,104 +22934,90 @@
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="M135" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N135" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O135" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R135" t="n">
-        <v>0.01778809170864137</v>
+        <v>0</v>
       </c>
       <c r="S135" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U135" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1540</t>
-        </is>
-      </c>
-      <c r="AA135" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO135" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP135" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ135" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS135" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1540</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR135" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS135" t="inlineStr"/>
       <c r="AT135" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU135" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV135" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ135" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA135" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB135" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC135" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -22958,17 +23044,17 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -23002,170 +23088,81 @@
         </is>
       </c>
       <c r="N136" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O136" t="n">
-        <v>1</v>
-      </c>
-      <c r="U136" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1540</t>
-        </is>
-      </c>
-      <c r="V136" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1540</t>
-        </is>
-      </c>
-      <c r="W136" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X136" t="inlineStr">
-        <is>
-          <t>Tularaemia (rabbit fever)</t>
-        </is>
-      </c>
-      <c r="Y136" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z136" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA136" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB136" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC136" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD136" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0</v>
+      </c>
+      <c r="S136" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO136" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP136" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR136" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS136" t="inlineStr"/>
+      <c r="AT136" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU136" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV136" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE136" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF136" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG136" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH136" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI136" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ136" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK136" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 1540.</t>
-        </is>
-      </c>
-      <c r="AM136" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN136" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO136" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP136" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ136" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS136" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1540</t>
-        </is>
-      </c>
-      <c r="AT136" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU136" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
-        </is>
-      </c>
-      <c r="AV136" t="inlineStr">
-        <is>
-          <t>thl_ttr</t>
-        </is>
-      </c>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ136" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA136" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB136" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC136" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -23197,12 +23194,12 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -23236,81 +23233,95 @@
         </is>
       </c>
       <c r="N137" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O137" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R137" t="n">
-        <v>0</v>
+        <v>0.01778809170864137</v>
       </c>
       <c r="S137" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U137" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1540</t>
+        </is>
+      </c>
+      <c r="AA137" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO137" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP137" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR137" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS137" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ137" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS137" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1540</t>
+        </is>
+      </c>
       <c r="AT137" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU137" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV137" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW137" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ137" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA137" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB137" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC137" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -23337,17 +23348,17 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -23381,22 +23392,39 @@
         </is>
       </c>
       <c r="N138" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O138" t="n">
-        <v>2</v>
-      </c>
-      <c r="R138" t="n">
-        <v>0.03537951651591013</v>
-      </c>
-      <c r="S138" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="U138" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_403_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1540</t>
+        </is>
+      </c>
+      <c r="V138" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1540</t>
+        </is>
+      </c>
+      <c r="W138" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X138" t="inlineStr">
+        <is>
+          <t>Tularaemia (rabbit fever)</t>
+        </is>
+      </c>
+      <c r="Y138" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z138" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
@@ -23404,6 +23432,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB138" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC138" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD138" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE138" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF138" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG138" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH138" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI138" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ138" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK138" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 1540.</t>
+        </is>
+      </c>
+      <c r="AM138" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN138" t="b">
+        <v>1</v>
+      </c>
       <c r="AO138" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -23416,12 +23502,12 @@
       </c>
       <c r="AQ138" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS138" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_403_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1540</t>
         </is>
       </c>
       <c r="AT138" t="n">
@@ -23429,47 +23515,47 @@
       </c>
       <c r="AU138" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV138" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW138" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ138" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA138" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB138" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC138" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -23496,17 +23582,17 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -23540,170 +23626,81 @@
         </is>
       </c>
       <c r="N139" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O139" t="n">
-        <v>2</v>
-      </c>
-      <c r="U139" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_403_MONTHLY</t>
-        </is>
-      </c>
-      <c r="V139" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_403_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W139" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X139" t="inlineStr">
-        <is>
-          <t>Tularemi</t>
-        </is>
-      </c>
-      <c r="Y139" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z139" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA139" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB139" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC139" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD139" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE139" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF139" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG139" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH139" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI139" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ139" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK139" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM139" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN139" t="b">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0</v>
+      </c>
+      <c r="S139" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO139" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP139" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ139" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS139" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_403_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR139" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS139" t="inlineStr"/>
       <c r="AT139" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU139" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV139" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ139" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA139" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB139" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC139" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -23735,12 +23732,12 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -23780,75 +23777,89 @@
         <v>2</v>
       </c>
       <c r="R140" t="n">
-        <v>0.0005730076265538771</v>
+        <v>0.03537951651591013</v>
       </c>
       <c r="S140" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U140" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_403_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA140" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO140" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP140" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR140" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS140" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ140" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS140" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_403_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT140" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU140" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV140" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ140" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA140" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB140" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC140" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -23875,17 +23886,17 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -23910,7 +23921,7 @@
       </c>
       <c r="L141" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M141" t="inlineStr">
@@ -23919,81 +23930,170 @@
         </is>
       </c>
       <c r="N141" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O141" t="n">
-        <v>0</v>
-      </c>
-      <c r="R141" t="n">
-        <v>0</v>
-      </c>
-      <c r="S141" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="U141" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_403_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V141" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_403_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W141" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X141" t="inlineStr">
+        <is>
+          <t>Tularemi</t>
+        </is>
+      </c>
+      <c r="Y141" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z141" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA141" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB141" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC141" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD141" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE141" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF141" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG141" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH141" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI141" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ141" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK141" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM141" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN141" t="b">
+        <v>1</v>
       </c>
       <c r="AO141" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP141" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR141" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS141" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ141" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS141" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_403_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT141" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU141" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV141" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW141" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ141" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA141" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB141" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC141" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -24055,7 +24155,7 @@
       </c>
       <c r="L142" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M142" t="inlineStr">
@@ -24137,6 +24237,296 @@
         </is>
       </c>
       <c r="BC142" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>D123</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>tularemia</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>Tularemia</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>D123</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>Tularemia</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>土拉菌病</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L143" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="M143" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N143" t="n">
+        <v>0</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0</v>
+      </c>
+      <c r="S143" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO143" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP143" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR143" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS143" t="inlineStr"/>
+      <c r="AT143" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU143" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV143" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW143" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX143" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY143" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ143" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA143" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB143" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC143" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>D123</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>tularemia</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>Tularemia</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>D123</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>Tularemia</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>土拉菌病</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L144" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="M144" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N144" t="n">
+        <v>2</v>
+      </c>
+      <c r="O144" t="n">
+        <v>2</v>
+      </c>
+      <c r="R144" t="n">
+        <v>0.0005730076265538771</v>
+      </c>
+      <c r="S144" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO144" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP144" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR144" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS144" t="inlineStr"/>
+      <c r="AT144" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU144" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV144" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW144" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX144" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY144" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ144" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA144" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB144" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC144" t="inlineStr">
         <is>
           <t>api; api</t>
         </is>
@@ -24258,7 +24648,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="10">
@@ -24268,7 +24658,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>141</v>
+        <v>143</v>
       </c>
     </row>
     <row r="11">
@@ -24288,7 +24678,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="13">

--- a/diseases/d123/2026-2029.xlsx
+++ b/diseases/d123/2026-2029.xlsx
@@ -24532,6 +24532,151 @@
         </is>
       </c>
     </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>D123</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>tularemia</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>Tularemia</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>D123</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>Tularemia</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>土拉菌病</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L145" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N145" t="n">
+        <v>0</v>
+      </c>
+      <c r="O145" t="n">
+        <v>0</v>
+      </c>
+      <c r="R145" t="n">
+        <v>0</v>
+      </c>
+      <c r="S145" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO145" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP145" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR145" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS145" t="inlineStr"/>
+      <c r="AT145" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU145" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV145" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW145" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX145" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY145" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ145" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA145" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB145" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC145" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -24565,7 +24710,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
     </row>
@@ -24648,7 +24793,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="10">
@@ -24658,7 +24803,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="11">

--- a/diseases/d123/2026-2029.xlsx
+++ b/diseases/d123/2026-2029.xlsx
@@ -4637,13 +4637,13 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R25" t="n">
-        <v>0.05550746142397953</v>
+        <v>0.06660895370877544</v>
       </c>
       <c r="S25" t="inlineStr">
         <is>
@@ -7828,13 +7828,13 @@
         </is>
       </c>
       <c r="N44" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O44" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="R44" t="n">
-        <v>0.06660895370877544</v>
+        <v>0.07771044599357135</v>
       </c>
       <c r="S44" t="inlineStr">
         <is>
@@ -11016,13 +11016,13 @@
         </is>
       </c>
       <c r="N63" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="O63" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="R63" t="n">
-        <v>0.1110149228479591</v>
+        <v>0.1332179074175509</v>
       </c>
       <c r="S63" t="inlineStr">
         <is>
@@ -14204,13 +14204,13 @@
         </is>
       </c>
       <c r="N82" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="O82" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="R82" t="n">
-        <v>0.2109283534111222</v>
+        <v>0.2220298456959181</v>
       </c>
       <c r="S82" t="inlineStr">
         <is>
@@ -17685,13 +17685,13 @@
         </is>
       </c>
       <c r="N103" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="O103" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="R103" t="n">
-        <v>0.1665223842719386</v>
+        <v>0.2331313379807141</v>
       </c>
       <c r="S103" t="inlineStr">
         <is>
@@ -20420,12 +20420,12 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -20459,95 +20459,81 @@
         </is>
       </c>
       <c r="N120" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="O120" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="R120" t="n">
-        <v>0.07115236683456549</v>
+        <v>0.1998268611263263</v>
       </c>
       <c r="S120" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U120" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1540</t>
-        </is>
-      </c>
-      <c r="AA120" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO120" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP120" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ120" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS120" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1540</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR120" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS120" t="inlineStr"/>
       <c r="AT120" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU120" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV120" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>foph_idd</t>
         </is>
       </c>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Switzerland FOPH IDD</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>rest_api</t>
         </is>
       </c>
       <c r="AZ120" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>foph_idd</t>
         </is>
       </c>
       <c r="BA120" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Switzerland FOPH IDD</t>
         </is>
       </c>
       <c r="BB120" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
         </is>
       </c>
       <c r="BC120" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>rest_api</t>
         </is>
       </c>
     </row>
@@ -20574,7 +20560,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -20623,98 +20609,23 @@
       <c r="O121" t="n">
         <v>4</v>
       </c>
+      <c r="R121" t="n">
+        <v>0.07115236683456549</v>
+      </c>
+      <c r="S121" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U121" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1540</t>
         </is>
       </c>
-      <c r="V121" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1540</t>
-        </is>
-      </c>
-      <c r="W121" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X121" t="inlineStr">
-        <is>
-          <t>Tularaemia (rabbit fever)</t>
-        </is>
-      </c>
-      <c r="Y121" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z121" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA121" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB121" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC121" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD121" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE121" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF121" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG121" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH121" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI121" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ121" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK121" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 1540.</t>
-        </is>
-      </c>
-      <c r="AM121" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN121" t="b">
-        <v>1</v>
       </c>
       <c r="AO121" t="inlineStr">
         <is>
@@ -20808,17 +20719,17 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -20852,81 +20763,170 @@
         </is>
       </c>
       <c r="N122" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O122" t="n">
-        <v>0</v>
-      </c>
-      <c r="R122" t="n">
-        <v>0</v>
-      </c>
-      <c r="S122" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>4</v>
+      </c>
+      <c r="U122" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1540</t>
+        </is>
+      </c>
+      <c r="V122" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1540</t>
+        </is>
+      </c>
+      <c r="W122" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X122" t="inlineStr">
+        <is>
+          <t>Tularaemia (rabbit fever)</t>
+        </is>
+      </c>
+      <c r="Y122" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z122" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA122" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB122" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC122" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD122" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE122" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF122" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG122" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH122" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI122" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ122" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK122" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 1540.</t>
+        </is>
+      </c>
+      <c r="AM122" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN122" t="b">
+        <v>1</v>
       </c>
       <c r="AO122" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP122" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR122" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS122" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ122" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS122" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1540</t>
+        </is>
+      </c>
       <c r="AT122" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU122" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV122" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ122" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA122" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB122" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC122" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -20958,12 +20958,12 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -20997,95 +20997,81 @@
         </is>
       </c>
       <c r="N123" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="O123" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="R123" t="n">
-        <v>0.1945873408375057</v>
+        <v>0</v>
       </c>
       <c r="S123" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U123" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_403_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA123" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO123" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP123" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ123" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS123" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_403_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR123" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS123" t="inlineStr"/>
       <c r="AT123" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU123" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV123" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ123" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA123" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB123" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC123" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -21112,7 +21098,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -21161,98 +21147,23 @@
       <c r="O124" t="n">
         <v>11</v>
       </c>
+      <c r="R124" t="n">
+        <v>0.1945873408375057</v>
+      </c>
+      <c r="S124" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U124" t="inlineStr">
         <is>
           <t>SER_NO_FHI_403_MONTHLY</t>
         </is>
       </c>
-      <c r="V124" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_403_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W124" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X124" t="inlineStr">
-        <is>
-          <t>Tularemi</t>
-        </is>
-      </c>
-      <c r="Y124" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z124" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA124" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB124" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC124" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD124" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE124" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF124" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG124" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH124" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI124" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ124" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK124" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM124" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN124" t="b">
-        <v>1</v>
       </c>
       <c r="AO124" t="inlineStr">
         <is>
@@ -21346,17 +21257,17 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -21390,22 +21301,39 @@
         </is>
       </c>
       <c r="N125" t="n">
-        <v>45</v>
+        <v>11</v>
       </c>
       <c r="O125" t="n">
-        <v>45</v>
-      </c>
-      <c r="R125" t="n">
-        <v>0.4205196192727506</v>
-      </c>
-      <c r="S125" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>11</v>
       </c>
       <c r="U125" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_TULAREMIA</t>
+          <t>SER_NO_FHI_403_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V125" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_403_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W125" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X125" t="inlineStr">
+        <is>
+          <t>Tularemi</t>
+        </is>
+      </c>
+      <c r="Y125" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z125" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
@@ -21413,6 +21341,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB125" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC125" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD125" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE125" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF125" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG125" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH125" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI125" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ125" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK125" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM125" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN125" t="b">
+        <v>1</v>
+      </c>
       <c r="AO125" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -21430,7 +21416,7 @@
       </c>
       <c r="AS125" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_TULAREMIA</t>
+          <t>SER_NO_FHI_403_MONTHLY</t>
         </is>
       </c>
       <c r="AT125" t="n">
@@ -21443,42 +21429,42 @@
       </c>
       <c r="AV125" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ125" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA125" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB125" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC125" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -21505,7 +21491,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -21554,98 +21540,23 @@
       <c r="O126" t="n">
         <v>45</v>
       </c>
+      <c r="R126" t="n">
+        <v>0.4205196192727506</v>
+      </c>
+      <c r="S126" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U126" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_TULAREMIA</t>
         </is>
       </c>
-      <c r="V126" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_TULAREMIA</t>
-        </is>
-      </c>
-      <c r="W126" t="inlineStr">
-        <is>
-          <t>SRC_SE_FOHM_SMINET</t>
-        </is>
-      </c>
-      <c r="X126" t="inlineStr">
-        <is>
-          <t>Harpest</t>
-        </is>
-      </c>
-      <c r="Y126" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z126" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA126" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB126" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC126" t="inlineStr">
-        <is>
-          <t>country:SE:national</t>
-        </is>
-      </c>
-      <c r="AD126" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE126" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF126" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG126" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH126" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI126" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ126" t="inlineStr">
-        <is>
-          <t>SE_FOHM_SMINET_current</t>
-        </is>
-      </c>
-      <c r="AK126" t="inlineStr">
-        <is>
-          <t>Sweden FHM SmiNet national monthly notification series; FHM tularemia category.</t>
-        </is>
-      </c>
-      <c r="AM126" t="inlineStr">
-        <is>
-          <t>revised</t>
-        </is>
-      </c>
-      <c r="AN126" t="b">
-        <v>1</v>
       </c>
       <c r="AO126" t="inlineStr">
         <is>
@@ -21739,17 +21650,17 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -21774,7 +21685,7 @@
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M127" t="inlineStr">
@@ -21783,81 +21694,170 @@
         </is>
       </c>
       <c r="N127" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="O127" t="n">
-        <v>0</v>
-      </c>
-      <c r="R127" t="n">
-        <v>0</v>
-      </c>
-      <c r="S127" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>45</v>
+      </c>
+      <c r="U127" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_TULAREMIA</t>
+        </is>
+      </c>
+      <c r="V127" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_TULAREMIA</t>
+        </is>
+      </c>
+      <c r="W127" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X127" t="inlineStr">
+        <is>
+          <t>Harpest</t>
+        </is>
+      </c>
+      <c r="Y127" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z127" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA127" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB127" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC127" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD127" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE127" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF127" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG127" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH127" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI127" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ127" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK127" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM tularemia category.</t>
+        </is>
+      </c>
+      <c r="AM127" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN127" t="b">
+        <v>1</v>
       </c>
       <c r="AO127" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP127" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR127" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS127" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ127" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS127" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_TULAREMIA</t>
+        </is>
+      </c>
       <c r="AT127" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU127" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV127" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ127" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA127" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB127" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC127" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -21889,12 +21889,12 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -21928,13 +21928,13 @@
         </is>
       </c>
       <c r="N128" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O128" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R128" t="n">
-        <v>0.0008595114398308156</v>
+        <v>0</v>
       </c>
       <c r="S128" t="inlineStr">
         <is>
@@ -21967,42 +21967,42 @@
       </c>
       <c r="AV128" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ128" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA128" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB128" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC128" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -22034,12 +22034,12 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -22064,7 +22064,7 @@
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="M129" t="inlineStr">
@@ -22073,13 +22073,13 @@
         </is>
       </c>
       <c r="N129" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O129" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R129" t="n">
-        <v>0</v>
+        <v>0.0008595114398308156</v>
       </c>
       <c r="S129" t="inlineStr">
         <is>
@@ -22112,42 +22112,42 @@
       </c>
       <c r="AV129" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ129" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA129" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB129" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC129" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -22179,12 +22179,12 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -22218,13 +22218,13 @@
         </is>
       </c>
       <c r="N130" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O130" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R130" t="n">
-        <v>0.0005730076265538771</v>
+        <v>0</v>
       </c>
       <c r="S130" t="inlineStr">
         <is>
@@ -22257,42 +22257,42 @@
       </c>
       <c r="AV130" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ130" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA130" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB130" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC130" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -22324,12 +22324,12 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -22354,7 +22354,7 @@
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="M131" t="inlineStr">
@@ -22363,13 +22363,13 @@
         </is>
       </c>
       <c r="N131" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O131" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R131" t="n">
-        <v>0</v>
+        <v>0.0005730076265538771</v>
       </c>
       <c r="S131" t="inlineStr">
         <is>
@@ -22402,42 +22402,42 @@
       </c>
       <c r="AV131" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ131" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA131" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB131" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC131" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -22469,12 +22469,12 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -22508,13 +22508,13 @@
         </is>
       </c>
       <c r="N132" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O132" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R132" t="n">
-        <v>0.0005730076265538771</v>
+        <v>0</v>
       </c>
       <c r="S132" t="inlineStr">
         <is>
@@ -22547,42 +22547,42 @@
       </c>
       <c r="AV132" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ132" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA132" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB132" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC132" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -22614,12 +22614,12 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -22644,7 +22644,7 @@
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="M133" t="inlineStr">
@@ -22653,13 +22653,13 @@
         </is>
       </c>
       <c r="N133" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O133" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R133" t="n">
-        <v>0</v>
+        <v>0.0005730076265538771</v>
       </c>
       <c r="S133" t="inlineStr">
         <is>
@@ -22692,42 +22692,42 @@
       </c>
       <c r="AV133" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ133" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA133" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB133" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC133" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -22759,12 +22759,12 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -22837,42 +22837,42 @@
       </c>
       <c r="AV134" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ134" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA134" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB134" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC134" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -22904,12 +22904,12 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -22934,7 +22934,7 @@
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="M135" t="inlineStr">
@@ -22982,42 +22982,42 @@
       </c>
       <c r="AV135" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ135" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA135" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB135" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC135" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -23049,12 +23049,12 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -23079,12 +23079,12 @@
       </c>
       <c r="L136" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N136" t="n">
@@ -23127,42 +23127,42 @@
       </c>
       <c r="AV136" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ136" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA136" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB136" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC136" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -23194,12 +23194,12 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -23233,95 +23233,81 @@
         </is>
       </c>
       <c r="N137" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O137" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R137" t="n">
-        <v>0.01778809170864137</v>
+        <v>0</v>
       </c>
       <c r="S137" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U137" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1540</t>
-        </is>
-      </c>
-      <c r="AA137" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO137" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP137" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ137" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS137" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1540</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR137" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS137" t="inlineStr"/>
       <c r="AT137" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU137" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV137" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW137" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ137" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA137" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB137" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC137" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -23348,7 +23334,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -23397,98 +23383,23 @@
       <c r="O138" t="n">
         <v>1</v>
       </c>
+      <c r="R138" t="n">
+        <v>0.01778809170864137</v>
+      </c>
+      <c r="S138" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U138" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1540</t>
         </is>
       </c>
-      <c r="V138" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1540</t>
-        </is>
-      </c>
-      <c r="W138" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X138" t="inlineStr">
-        <is>
-          <t>Tularaemia (rabbit fever)</t>
-        </is>
-      </c>
-      <c r="Y138" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z138" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA138" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB138" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC138" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD138" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE138" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF138" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG138" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH138" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI138" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ138" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK138" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 1540.</t>
-        </is>
-      </c>
-      <c r="AM138" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN138" t="b">
-        <v>1</v>
       </c>
       <c r="AO138" t="inlineStr">
         <is>
@@ -23582,17 +23493,17 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -23626,81 +23537,170 @@
         </is>
       </c>
       <c r="N139" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O139" t="n">
-        <v>0</v>
-      </c>
-      <c r="R139" t="n">
-        <v>0</v>
-      </c>
-      <c r="S139" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="U139" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1540</t>
+        </is>
+      </c>
+      <c r="V139" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1540</t>
+        </is>
+      </c>
+      <c r="W139" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X139" t="inlineStr">
+        <is>
+          <t>Tularaemia (rabbit fever)</t>
+        </is>
+      </c>
+      <c r="Y139" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z139" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA139" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB139" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC139" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD139" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE139" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF139" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG139" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH139" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI139" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ139" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK139" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 1540.</t>
+        </is>
+      </c>
+      <c r="AM139" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN139" t="b">
+        <v>1</v>
       </c>
       <c r="AO139" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP139" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR139" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS139" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ139" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS139" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1540</t>
+        </is>
+      </c>
       <c r="AT139" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU139" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV139" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ139" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA139" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB139" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC139" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -23732,12 +23732,12 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -23771,95 +23771,81 @@
         </is>
       </c>
       <c r="N140" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O140" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R140" t="n">
-        <v>0.03537951651591013</v>
+        <v>0</v>
       </c>
       <c r="S140" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U140" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_403_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA140" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO140" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP140" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ140" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS140" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_403_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR140" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS140" t="inlineStr"/>
       <c r="AT140" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU140" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV140" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ140" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA140" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB140" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC140" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -23886,7 +23872,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -23930,103 +23916,28 @@
         </is>
       </c>
       <c r="N141" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="O141" t="n">
-        <v>2</v>
+        <v>11</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.1945873408375057</v>
+      </c>
+      <c r="S141" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="U141" t="inlineStr">
         <is>
           <t>SER_NO_FHI_403_MONTHLY</t>
         </is>
       </c>
-      <c r="V141" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_403_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W141" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X141" t="inlineStr">
-        <is>
-          <t>Tularemi</t>
-        </is>
-      </c>
-      <c r="Y141" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z141" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA141" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB141" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC141" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD141" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE141" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF141" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG141" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH141" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI141" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ141" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK141" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM141" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN141" t="b">
-        <v>1</v>
       </c>
       <c r="AO141" t="inlineStr">
         <is>
@@ -24120,17 +24031,17 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -24164,81 +24075,170 @@
         </is>
       </c>
       <c r="N142" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="O142" t="n">
-        <v>2</v>
-      </c>
-      <c r="R142" t="n">
-        <v>0.0005730076265538771</v>
-      </c>
-      <c r="S142" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>11</v>
+      </c>
+      <c r="U142" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_403_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V142" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_403_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W142" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X142" t="inlineStr">
+        <is>
+          <t>Tularemi</t>
+        </is>
+      </c>
+      <c r="Y142" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z142" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA142" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB142" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC142" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD142" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE142" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF142" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG142" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH142" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI142" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ142" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK142" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM142" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN142" t="b">
+        <v>1</v>
       </c>
       <c r="AO142" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP142" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR142" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS142" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ142" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS142" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_403_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT142" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU142" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV142" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW142" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX142" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY142" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ142" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA142" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB142" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC142" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -24270,12 +24270,12 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -24300,7 +24300,7 @@
       </c>
       <c r="L143" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M143" t="inlineStr">
@@ -24309,13 +24309,13 @@
         </is>
       </c>
       <c r="N143" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O143" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R143" t="n">
-        <v>0</v>
+        <v>0.0005730076265538771</v>
       </c>
       <c r="S143" t="inlineStr">
         <is>
@@ -24348,42 +24348,42 @@
       </c>
       <c r="AV143" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW143" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ143" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA143" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB143" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC143" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -24415,12 +24415,12 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -24445,7 +24445,7 @@
       </c>
       <c r="L144" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M144" t="inlineStr">
@@ -24454,13 +24454,13 @@
         </is>
       </c>
       <c r="N144" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O144" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R144" t="n">
-        <v>0.0005730076265538771</v>
+        <v>0</v>
       </c>
       <c r="S144" t="inlineStr">
         <is>
@@ -24493,42 +24493,42 @@
       </c>
       <c r="AV144" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW144" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX144" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY144" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ144" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA144" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB144" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC144" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -24560,12 +24560,12 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -24590,7 +24590,7 @@
       </c>
       <c r="L145" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="M145" t="inlineStr">
@@ -24599,13 +24599,13 @@
         </is>
       </c>
       <c r="N145" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O145" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R145" t="n">
-        <v>0</v>
+        <v>0.0005730076265538771</v>
       </c>
       <c r="S145" t="inlineStr">
         <is>
@@ -24638,42 +24638,332 @@
       </c>
       <c r="AV145" t="inlineStr">
         <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW145" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX145" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY145" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ145" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA145" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB145" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC145" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>D123</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>tularemia</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>Tularemia</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>D123</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>Tularemia</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>土拉菌病</t>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L146" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="M146" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N146" t="n">
+        <v>0</v>
+      </c>
+      <c r="O146" t="n">
+        <v>0</v>
+      </c>
+      <c r="R146" t="n">
+        <v>0</v>
+      </c>
+      <c r="S146" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO146" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP146" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR146" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS146" t="inlineStr"/>
+      <c r="AT146" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU146" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV146" t="inlineStr">
+        <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="AW145" t="inlineStr">
+      <c r="AW146" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="AX145" t="inlineStr">
+      <c r="AX146" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="AY145" t="inlineStr">
+      <c r="AY146" t="inlineStr">
         <is>
           <t>web</t>
         </is>
       </c>
-      <c r="AZ145" t="inlineStr">
+      <c r="AZ146" t="inlineStr">
         <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="BA145" t="inlineStr">
+      <c r="BA146" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="BB145" t="inlineStr">
+      <c r="BB146" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="BC145" t="inlineStr">
+      <c r="BC146" t="inlineStr">
         <is>
           <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>D123</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>tularemia</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>Tularemia</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>D123</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>Tularemia</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>土拉菌病</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L147" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="M147" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N147" t="n">
+        <v>5</v>
+      </c>
+      <c r="O147" t="n">
+        <v>5</v>
+      </c>
+      <c r="R147" t="n">
+        <v>0.001432519066384693</v>
+      </c>
+      <c r="S147" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO147" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP147" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR147" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS147" t="inlineStr"/>
+      <c r="AT147" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU147" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV147" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW147" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX147" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY147" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ147" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA147" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB147" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC147" t="inlineStr">
+        <is>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -24710,7 +25000,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
@@ -24793,7 +25083,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="10">
@@ -24803,7 +25093,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="11">
@@ -24855,7 +25145,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>212</v>
+        <v>255</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d123/2026-2029.xlsx
+++ b/diseases/d123/2026-2029.xlsx
@@ -23378,13 +23378,13 @@
         </is>
       </c>
       <c r="N138" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="O138" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="R138" t="n">
-        <v>0.01778809170864137</v>
+        <v>0.142304733669131</v>
       </c>
       <c r="S138" t="inlineStr">
         <is>
@@ -23537,10 +23537,10 @@
         </is>
       </c>
       <c r="N139" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="O139" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="U139" t="inlineStr">
         <is>
@@ -23916,13 +23916,13 @@
         </is>
       </c>
       <c r="N141" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="O141" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="R141" t="n">
-        <v>0.1945873408375057</v>
+        <v>0.3537951651591013</v>
       </c>
       <c r="S141" t="inlineStr">
         <is>
@@ -24075,10 +24075,10 @@
         </is>
       </c>
       <c r="N142" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="O142" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="U142" t="inlineStr">
         <is>
@@ -24964,6 +24964,151 @@
       <c r="BC147" t="inlineStr">
         <is>
           <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>D123</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>tularemia</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>Tularemia</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>D123</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>Tularemia</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>土拉菌病</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L148" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="M148" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N148" t="n">
+        <v>0</v>
+      </c>
+      <c r="O148" t="n">
+        <v>0</v>
+      </c>
+      <c r="R148" t="n">
+        <v>0</v>
+      </c>
+      <c r="S148" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO148" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP148" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR148" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS148" t="inlineStr"/>
+      <c r="AT148" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU148" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV148" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW148" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX148" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY148" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ148" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA148" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB148" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC148" t="inlineStr">
+        <is>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -25000,7 +25145,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -25083,7 +25228,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="10">
@@ -25093,7 +25238,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="11">
@@ -25145,7 +25290,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>255</v>
+        <v>271</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d123/2026-2029.xlsx
+++ b/diseases/d123/2026-2029.xlsx
@@ -25112,6 +25112,151 @@
         </is>
       </c>
     </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>D123</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>tularemia</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>Tularemia</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>D123</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>Tularemia</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>土拉菌病</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L149" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N149" t="n">
+        <v>2</v>
+      </c>
+      <c r="O149" t="n">
+        <v>2</v>
+      </c>
+      <c r="R149" t="n">
+        <v>0.0005730076265538771</v>
+      </c>
+      <c r="S149" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO149" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP149" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR149" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS149" t="inlineStr"/>
+      <c r="AT149" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU149" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV149" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW149" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX149" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY149" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ149" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA149" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB149" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC149" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -25145,7 +25290,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
@@ -25228,7 +25373,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="10">
@@ -25238,7 +25383,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="11">
@@ -25290,7 +25435,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d123/2026-2029.xlsx
+++ b/diseases/d123/2026-2029.xlsx
@@ -1473,7 +1473,7 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
@@ -1481,17 +1481,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS6" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1540</t>
         </is>
       </c>
       <c r="AT6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
@@ -1707,7 +1712,7 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
@@ -1715,17 +1720,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS7" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1540</t>
         </is>
       </c>
       <c r="AT7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
@@ -2011,7 +2021,7 @@
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
@@ -2019,17 +2029,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS9" t="inlineStr">
         <is>
           <t>SER_NO_FHI_403_MONTHLY</t>
         </is>
       </c>
       <c r="AT9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
@@ -2245,7 +2260,7 @@
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
@@ -2253,17 +2268,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS10" t="inlineStr">
         <is>
           <t>SER_NO_FHI_403_MONTHLY</t>
         </is>
       </c>
       <c r="AT10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
@@ -2404,7 +2424,7 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
@@ -2412,17 +2432,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR11" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS11" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_TULAREMIA</t>
         </is>
       </c>
       <c r="AT11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
@@ -2638,7 +2663,7 @@
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
@@ -2646,17 +2671,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR12" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS12" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_TULAREMIA</t>
         </is>
       </c>
       <c r="AT12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
@@ -4812,7 +4842,7 @@
       </c>
       <c r="AP26" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ26" t="inlineStr">
@@ -4820,17 +4850,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR26" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS26" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1540</t>
         </is>
       </c>
       <c r="AT26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU26" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV26" t="inlineStr">
@@ -5046,7 +5081,7 @@
       </c>
       <c r="AP27" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ27" t="inlineStr">
@@ -5054,17 +5089,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR27" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS27" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1540</t>
         </is>
       </c>
       <c r="AT27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU27" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV27" t="inlineStr">
@@ -5350,7 +5390,7 @@
       </c>
       <c r="AP29" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ29" t="inlineStr">
@@ -5358,17 +5398,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR29" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS29" t="inlineStr">
         <is>
           <t>SER_NO_FHI_403_MONTHLY</t>
         </is>
       </c>
       <c r="AT29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU29" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV29" t="inlineStr">
@@ -5584,7 +5629,7 @@
       </c>
       <c r="AP30" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ30" t="inlineStr">
@@ -5592,17 +5637,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR30" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS30" t="inlineStr">
         <is>
           <t>SER_NO_FHI_403_MONTHLY</t>
         </is>
       </c>
       <c r="AT30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU30" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV30" t="inlineStr">
@@ -5743,7 +5793,7 @@
       </c>
       <c r="AP31" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ31" t="inlineStr">
@@ -5751,17 +5801,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR31" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS31" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_TULAREMIA</t>
         </is>
       </c>
       <c r="AT31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU31" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV31" t="inlineStr">
@@ -5977,7 +6032,7 @@
       </c>
       <c r="AP32" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ32" t="inlineStr">
@@ -5985,17 +6040,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR32" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS32" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_TULAREMIA</t>
         </is>
       </c>
       <c r="AT32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU32" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV32" t="inlineStr">
@@ -8003,7 +8063,7 @@
       </c>
       <c r="AP45" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ45" t="inlineStr">
@@ -8011,17 +8071,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR45" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS45" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1540</t>
         </is>
       </c>
       <c r="AT45" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU45" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV45" t="inlineStr">
@@ -8237,7 +8302,7 @@
       </c>
       <c r="AP46" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ46" t="inlineStr">
@@ -8245,17 +8310,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR46" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS46" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1540</t>
         </is>
       </c>
       <c r="AT46" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU46" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV46" t="inlineStr">
@@ -8541,7 +8611,7 @@
       </c>
       <c r="AP48" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ48" t="inlineStr">
@@ -8549,17 +8619,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR48" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS48" t="inlineStr">
         <is>
           <t>SER_NO_FHI_403_MONTHLY</t>
         </is>
       </c>
       <c r="AT48" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU48" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV48" t="inlineStr">
@@ -8775,7 +8850,7 @@
       </c>
       <c r="AP49" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ49" t="inlineStr">
@@ -8783,17 +8858,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR49" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS49" t="inlineStr">
         <is>
           <t>SER_NO_FHI_403_MONTHLY</t>
         </is>
       </c>
       <c r="AT49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU49" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV49" t="inlineStr">
@@ -8934,7 +9014,7 @@
       </c>
       <c r="AP50" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ50" t="inlineStr">
@@ -8942,17 +9022,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR50" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS50" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_TULAREMIA</t>
         </is>
       </c>
       <c r="AT50" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU50" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV50" t="inlineStr">
@@ -9168,7 +9253,7 @@
       </c>
       <c r="AP51" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ51" t="inlineStr">
@@ -9176,17 +9261,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR51" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS51" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_TULAREMIA</t>
         </is>
       </c>
       <c r="AT51" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU51" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV51" t="inlineStr">
@@ -11191,7 +11281,7 @@
       </c>
       <c r="AP64" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ64" t="inlineStr">
@@ -11199,17 +11289,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR64" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS64" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1540</t>
         </is>
       </c>
       <c r="AT64" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU64" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV64" t="inlineStr">
@@ -11425,7 +11520,7 @@
       </c>
       <c r="AP65" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ65" t="inlineStr">
@@ -11433,17 +11528,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR65" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS65" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1540</t>
         </is>
       </c>
       <c r="AT65" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU65" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV65" t="inlineStr">
@@ -11729,7 +11829,7 @@
       </c>
       <c r="AP67" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ67" t="inlineStr">
@@ -11737,17 +11837,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR67" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS67" t="inlineStr">
         <is>
           <t>SER_NO_FHI_403_MONTHLY</t>
         </is>
       </c>
       <c r="AT67" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU67" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV67" t="inlineStr">
@@ -11963,7 +12068,7 @@
       </c>
       <c r="AP68" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ68" t="inlineStr">
@@ -11971,17 +12076,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR68" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS68" t="inlineStr">
         <is>
           <t>SER_NO_FHI_403_MONTHLY</t>
         </is>
       </c>
       <c r="AT68" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU68" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV68" t="inlineStr">
@@ -12122,7 +12232,7 @@
       </c>
       <c r="AP69" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ69" t="inlineStr">
@@ -12130,17 +12240,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR69" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS69" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_TULAREMIA</t>
         </is>
       </c>
       <c r="AT69" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU69" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV69" t="inlineStr">
@@ -12356,7 +12471,7 @@
       </c>
       <c r="AP70" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ70" t="inlineStr">
@@ -12364,17 +12479,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR70" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS70" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_TULAREMIA</t>
         </is>
       </c>
       <c r="AT70" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU70" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV70" t="inlineStr">
@@ -14379,7 +14499,7 @@
       </c>
       <c r="AP83" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ83" t="inlineStr">
@@ -14387,17 +14507,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR83" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS83" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1540</t>
         </is>
       </c>
       <c r="AT83" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU83" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV83" t="inlineStr">
@@ -14613,7 +14738,7 @@
       </c>
       <c r="AP84" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ84" t="inlineStr">
@@ -14621,17 +14746,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR84" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS84" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1540</t>
         </is>
       </c>
       <c r="AT84" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU84" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV84" t="inlineStr">
@@ -14917,7 +15047,7 @@
       </c>
       <c r="AP86" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ86" t="inlineStr">
@@ -14925,17 +15055,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR86" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS86" t="inlineStr">
         <is>
           <t>SER_NO_FHI_403_MONTHLY</t>
         </is>
       </c>
       <c r="AT86" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU86" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV86" t="inlineStr">
@@ -15151,7 +15286,7 @@
       </c>
       <c r="AP87" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ87" t="inlineStr">
@@ -15159,17 +15294,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR87" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS87" t="inlineStr">
         <is>
           <t>SER_NO_FHI_403_MONTHLY</t>
         </is>
       </c>
       <c r="AT87" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU87" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV87" t="inlineStr">
@@ -15310,7 +15450,7 @@
       </c>
       <c r="AP88" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ88" t="inlineStr">
@@ -15318,17 +15458,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR88" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS88" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_TULAREMIA</t>
         </is>
       </c>
       <c r="AT88" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU88" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV88" t="inlineStr">
@@ -15544,7 +15689,7 @@
       </c>
       <c r="AP89" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ89" t="inlineStr">
@@ -15552,17 +15697,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR89" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS89" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_TULAREMIA</t>
         </is>
       </c>
       <c r="AT89" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU89" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV89" t="inlineStr">
@@ -17860,7 +18010,7 @@
       </c>
       <c r="AP104" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ104" t="inlineStr">
@@ -17868,17 +18018,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR104" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS104" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1540</t>
         </is>
       </c>
       <c r="AT104" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU104" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV104" t="inlineStr">
@@ -18094,7 +18249,7 @@
       </c>
       <c r="AP105" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ105" t="inlineStr">
@@ -18102,17 +18257,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR105" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS105" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1540</t>
         </is>
       </c>
       <c r="AT105" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU105" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV105" t="inlineStr">
@@ -18398,7 +18558,7 @@
       </c>
       <c r="AP107" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ107" t="inlineStr">
@@ -18406,17 +18566,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR107" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS107" t="inlineStr">
         <is>
           <t>SER_NO_FHI_403_MONTHLY</t>
         </is>
       </c>
       <c r="AT107" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU107" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV107" t="inlineStr">
@@ -18632,7 +18797,7 @@
       </c>
       <c r="AP108" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ108" t="inlineStr">
@@ -18640,17 +18805,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR108" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS108" t="inlineStr">
         <is>
           <t>SER_NO_FHI_403_MONTHLY</t>
         </is>
       </c>
       <c r="AT108" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU108" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV108" t="inlineStr">
@@ -18791,7 +18961,7 @@
       </c>
       <c r="AP109" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ109" t="inlineStr">
@@ -18799,17 +18969,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR109" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS109" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_TULAREMIA</t>
         </is>
       </c>
       <c r="AT109" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU109" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV109" t="inlineStr">
@@ -19025,7 +19200,7 @@
       </c>
       <c r="AP110" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ110" t="inlineStr">
@@ -19033,17 +19208,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR110" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS110" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_TULAREMIA</t>
         </is>
       </c>
       <c r="AT110" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU110" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV110" t="inlineStr">
@@ -20634,7 +20814,7 @@
       </c>
       <c r="AP121" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ121" t="inlineStr">
@@ -20642,17 +20822,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR121" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS121" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1540</t>
         </is>
       </c>
       <c r="AT121" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU121" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV121" t="inlineStr">
@@ -20868,7 +21053,7 @@
       </c>
       <c r="AP122" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ122" t="inlineStr">
@@ -20876,17 +21061,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR122" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS122" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1540</t>
         </is>
       </c>
       <c r="AT122" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU122" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV122" t="inlineStr">
@@ -21172,7 +21362,7 @@
       </c>
       <c r="AP124" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ124" t="inlineStr">
@@ -21180,17 +21370,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR124" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS124" t="inlineStr">
         <is>
           <t>SER_NO_FHI_403_MONTHLY</t>
         </is>
       </c>
       <c r="AT124" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU124" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV124" t="inlineStr">
@@ -21406,7 +21601,7 @@
       </c>
       <c r="AP125" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ125" t="inlineStr">
@@ -21414,17 +21609,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR125" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS125" t="inlineStr">
         <is>
           <t>SER_NO_FHI_403_MONTHLY</t>
         </is>
       </c>
       <c r="AT125" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU125" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV125" t="inlineStr">
@@ -21565,7 +21765,7 @@
       </c>
       <c r="AP126" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ126" t="inlineStr">
@@ -21573,17 +21773,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR126" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS126" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_TULAREMIA</t>
         </is>
       </c>
       <c r="AT126" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU126" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV126" t="inlineStr">
@@ -21799,7 +22004,7 @@
       </c>
       <c r="AP127" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ127" t="inlineStr">
@@ -21807,17 +22012,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR127" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS127" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_TULAREMIA</t>
         </is>
       </c>
       <c r="AT127" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU127" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV127" t="inlineStr">
@@ -23408,7 +23618,7 @@
       </c>
       <c r="AP138" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ138" t="inlineStr">
@@ -23416,17 +23626,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR138" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS138" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1540</t>
         </is>
       </c>
       <c r="AT138" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU138" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV138" t="inlineStr">
@@ -23642,7 +23857,7 @@
       </c>
       <c r="AP139" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ139" t="inlineStr">
@@ -23650,17 +23865,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR139" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS139" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1540</t>
         </is>
       </c>
       <c r="AT139" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU139" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV139" t="inlineStr">
@@ -23946,7 +24166,7 @@
       </c>
       <c r="AP141" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ141" t="inlineStr">
@@ -23954,17 +24174,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR141" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS141" t="inlineStr">
         <is>
           <t>SER_NO_FHI_403_MONTHLY</t>
         </is>
       </c>
       <c r="AT141" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU141" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV141" t="inlineStr">
@@ -24180,7 +24405,7 @@
       </c>
       <c r="AP142" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ142" t="inlineStr">
@@ -24188,17 +24413,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR142" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS142" t="inlineStr">
         <is>
           <t>SER_NO_FHI_403_MONTHLY</t>
         </is>
       </c>
       <c r="AT142" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU142" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV142" t="inlineStr">
